--- a/payments.xlsx
+++ b/payments.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G8"/>
   <cols>
     <col min="1" max="1" width="28.83203125" customWidth="1"/>
     <col min="2" max="2" width="25.83203125" customWidth="1"/>
@@ -433,53 +433,168 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>686e24d32f21c9417882f777</v>
+        <v>6878c1edcdcb91aacab49c6b</v>
       </c>
       <c r="B2" t="str">
-        <v>unknowne1931</v>
-      </c>
-      <c r="C2">
+        <v>gn3391744</v>
+      </c>
+      <c r="C2" t="str">
+        <v>20₹</v>
+      </c>
+      <c r="D2">
         <v>0</v>
       </c>
-      <c r="D2">
-        <v>10</v>
-      </c>
-      <c r="E2">
-        <v>-10</v>
+      <c r="E2" t="str">
+        <v>020₹</v>
       </c>
       <c r="F2" t="str">
-        <v>To start Mili Game</v>
+        <v>Paid to Bank Account or UPI</v>
       </c>
       <c r="G2" t="str">
-        <v>17/08/2026, 19:29:16</v>
+        <v>17/08/2026, 21:23:47</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
+        <v>6878c1edcdcb91aacab49c6b</v>
+      </c>
+      <c r="B3" t="str">
+        <v>gn3391744</v>
+      </c>
+      <c r="C3" t="str">
+        <v>20₹</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3" t="str">
+        <v>2020₹</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Paid to Bank Account or UPI</v>
+      </c>
+      <c r="G3" t="str">
+        <v>17/08/2026, 21:24:43</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
         <v>686e24d32f21c9417882f777</v>
       </c>
-      <c r="B3" t="str">
+      <c r="B4" t="str">
         <v>unknowne1931</v>
       </c>
-      <c r="C3">
+      <c r="C4" t="str">
+        <v>50₹</v>
+      </c>
+      <c r="D4">
         <v>0</v>
       </c>
-      <c r="D3">
-        <v>10</v>
-      </c>
-      <c r="E3">
-        <v>-20</v>
-      </c>
-      <c r="F3" t="str">
-        <v>To start Mili Game</v>
-      </c>
-      <c r="G3" t="str">
-        <v>17/08/2026, 19:29:54</v>
+      <c r="E4" t="str">
+        <v>202050₹</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Paid to Bank Account or UPI</v>
+      </c>
+      <c r="G4" t="str">
+        <v>17/08/2026, 21:24:51</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>6878c1edcdcb91aacab49c6b</v>
+      </c>
+      <c r="B5" t="str">
+        <v>gn3391744</v>
+      </c>
+      <c r="C5" t="str">
+        <v>20</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5" t="str">
+        <v>20205020</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Paid to Bank Account or UPI</v>
+      </c>
+      <c r="G5" t="str">
+        <v>17/08/2026, 21:27:47</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>6878c1edcdcb91aacab49c6b</v>
+      </c>
+      <c r="B6" t="str">
+        <v>gn3391744</v>
+      </c>
+      <c r="C6" t="str">
+        <v>20</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6" t="str">
+        <v>2020502020</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Paid to Bank Account or UPI</v>
+      </c>
+      <c r="G6" t="str">
+        <v>17/08/2026, 21:27:51</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B7" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C7" t="str">
+        <v>50</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7" t="str">
+        <v>202050202050</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Paid to Bank Account or UPI</v>
+      </c>
+      <c r="G7" t="str">
+        <v>17/08/2026, 21:27:54</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B8" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C8" t="str">
+        <v>20</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8" t="str">
+        <v>20205020205020</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Paid to Bank Account or UPI</v>
+      </c>
+      <c r="G8" t="str">
+        <v>17/08/2026, 21:27:59</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G8"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/payments.xlsx
+++ b/payments.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G10"/>
   <cols>
     <col min="1" max="1" width="28.83203125" customWidth="1"/>
     <col min="2" max="2" width="25.83203125" customWidth="1"/>
@@ -592,9 +592,55 @@
         <v>17/08/2026, 21:27:59</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B9" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>10</v>
+      </c>
+      <c r="E9">
+        <v>20205020205010</v>
+      </c>
+      <c r="F9" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G9" t="str">
+        <v>18/08/2026, 13:12:20</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B10" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>10</v>
+      </c>
+      <c r="E10">
+        <v>20205020205000</v>
+      </c>
+      <c r="F10" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G10" t="str">
+        <v>18/08/2026, 13:15:13</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G10"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/payments.xlsx
+++ b/payments.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G41"/>
   <cols>
     <col min="1" max="1" width="28.83203125" customWidth="1"/>
     <col min="2" max="2" width="25.83203125" customWidth="1"/>
@@ -638,9 +638,722 @@
         <v>18/08/2026, 13:15:13</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B11" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>10</v>
+      </c>
+      <c r="E11">
+        <v>20205020204990</v>
+      </c>
+      <c r="F11" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G11" t="str">
+        <v>18/08/2026, 17:49:43</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B12" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>10</v>
+      </c>
+      <c r="E12">
+        <v>20205020204980</v>
+      </c>
+      <c r="F12" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G12" t="str">
+        <v>18/08/2026, 17:50:27</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B13" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>10</v>
+      </c>
+      <c r="E13" t="str">
+        <v>970</v>
+      </c>
+      <c r="F13" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G13" t="str">
+        <v>18/08/2026, 18:02:44</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B14" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>10</v>
+      </c>
+      <c r="E14" t="str">
+        <v>960</v>
+      </c>
+      <c r="F14" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G14" t="str">
+        <v>18/08/2026, 18:20:50</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B15" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>10</v>
+      </c>
+      <c r="E15" t="str">
+        <v>950</v>
+      </c>
+      <c r="F15" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G15" t="str">
+        <v>18/08/2026, 18:26:55</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B16" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>10</v>
+      </c>
+      <c r="E16" t="str">
+        <v>940</v>
+      </c>
+      <c r="F16" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G16" t="str">
+        <v>18/08/2026, 18:30:06</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B17" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>10</v>
+      </c>
+      <c r="E17" t="str">
+        <v>930</v>
+      </c>
+      <c r="F17" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G17" t="str">
+        <v>18/08/2026, 18:31:03</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B18" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>10</v>
+      </c>
+      <c r="E18" t="str">
+        <v>920</v>
+      </c>
+      <c r="F18" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G18" t="str">
+        <v>18/08/2026, 18:33:47</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B19" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>10</v>
+      </c>
+      <c r="E19" t="str">
+        <v>910</v>
+      </c>
+      <c r="F19" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G19" t="str">
+        <v>18/08/2026, 20:18:03</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B20" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>10</v>
+      </c>
+      <c r="E20" t="str">
+        <v>900</v>
+      </c>
+      <c r="F20" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G20" t="str">
+        <v>18/08/2026, 20:23:54</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B21" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>10</v>
+      </c>
+      <c r="E21" t="str">
+        <v>890</v>
+      </c>
+      <c r="F21" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G21" t="str">
+        <v>18/08/2026, 20:24:29</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B22" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>10</v>
+      </c>
+      <c r="E22" t="str">
+        <v>880</v>
+      </c>
+      <c r="F22" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G22" t="str">
+        <v>19/08/2026, 08:42:22</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B23" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>10</v>
+      </c>
+      <c r="E23" t="str">
+        <v>870</v>
+      </c>
+      <c r="F23" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G23" t="str">
+        <v>19/08/2026, 08:43:37</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B24" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>10</v>
+      </c>
+      <c r="E24" t="str">
+        <v>860</v>
+      </c>
+      <c r="F24" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G24" t="str">
+        <v>19/08/2026, 10:37:26</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B25" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>10</v>
+      </c>
+      <c r="E25" t="str">
+        <v>850</v>
+      </c>
+      <c r="F25" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G25" t="str">
+        <v>19/08/2026, 10:52:45</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B26" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <v>10</v>
+      </c>
+      <c r="E26" t="str">
+        <v>840</v>
+      </c>
+      <c r="F26" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G26" t="str">
+        <v>19/08/2026, 13:32:44</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B27" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <v>10</v>
+      </c>
+      <c r="E27" t="str">
+        <v>830</v>
+      </c>
+      <c r="F27" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G27" t="str">
+        <v>19/08/2026, 13:45:55</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B28" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28">
+        <v>10</v>
+      </c>
+      <c r="E28" t="str">
+        <v>820</v>
+      </c>
+      <c r="F28" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G28" t="str">
+        <v>19/08/2026, 13:46:50</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B29" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
+      <c r="D29">
+        <v>10</v>
+      </c>
+      <c r="E29" t="str">
+        <v>810</v>
+      </c>
+      <c r="F29" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G29" t="str">
+        <v>19/08/2026, 13:47:43</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B30" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
+      <c r="D30">
+        <v>10</v>
+      </c>
+      <c r="E30" t="str">
+        <v>800</v>
+      </c>
+      <c r="F30" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G30" t="str">
+        <v>19/08/2026, 13:49:48</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B31" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
+      <c r="D31">
+        <v>10</v>
+      </c>
+      <c r="E31" t="str">
+        <v>790</v>
+      </c>
+      <c r="F31" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G31" t="str">
+        <v>19/08/2026, 13:55:14</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B32" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C32">
+        <v>0</v>
+      </c>
+      <c r="D32">
+        <v>10</v>
+      </c>
+      <c r="E32" t="str">
+        <v>780</v>
+      </c>
+      <c r="F32" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G32" t="str">
+        <v>19/08/2026, 14:02:57</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B33" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C33">
+        <v>0</v>
+      </c>
+      <c r="D33">
+        <v>10</v>
+      </c>
+      <c r="E33" t="str">
+        <v>770</v>
+      </c>
+      <c r="F33" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G33" t="str">
+        <v>19/08/2026, 14:17:28</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B34" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C34">
+        <v>0</v>
+      </c>
+      <c r="D34">
+        <v>10</v>
+      </c>
+      <c r="E34" t="str">
+        <v>760</v>
+      </c>
+      <c r="F34" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G34" t="str">
+        <v>19/08/2026, 14:21:09</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B35" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
+      <c r="D35">
+        <v>10</v>
+      </c>
+      <c r="E35" t="str">
+        <v>750</v>
+      </c>
+      <c r="F35" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G35" t="str">
+        <v>19/08/2026, 14:26:57</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B36" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C36">
+        <v>0</v>
+      </c>
+      <c r="D36">
+        <v>10</v>
+      </c>
+      <c r="E36" t="str">
+        <v>740</v>
+      </c>
+      <c r="F36" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G36" t="str">
+        <v>19/08/2026, 14:38:48</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B37" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C37">
+        <v>0</v>
+      </c>
+      <c r="D37">
+        <v>10</v>
+      </c>
+      <c r="E37" t="str">
+        <v>730</v>
+      </c>
+      <c r="F37" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G37" t="str">
+        <v>19/08/2026, 14:44:50</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B38" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C38">
+        <v>0</v>
+      </c>
+      <c r="D38">
+        <v>10</v>
+      </c>
+      <c r="E38" t="str">
+        <v>720</v>
+      </c>
+      <c r="F38" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G38" t="str">
+        <v>19/08/2026, 15:02:55</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B39" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C39">
+        <v>0</v>
+      </c>
+      <c r="D39">
+        <v>10</v>
+      </c>
+      <c r="E39" t="str">
+        <v>710</v>
+      </c>
+      <c r="F39" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G39" t="str">
+        <v>19/08/2026, 15:14:13</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B40" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C40">
+        <v>0</v>
+      </c>
+      <c r="D40">
+        <v>10</v>
+      </c>
+      <c r="E40" t="str">
+        <v>700</v>
+      </c>
+      <c r="F40" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G40" t="str">
+        <v>19/08/2026, 15:21:42</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B41" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C41">
+        <v>0</v>
+      </c>
+      <c r="D41">
+        <v>10</v>
+      </c>
+      <c r="E41" t="str">
+        <v>690</v>
+      </c>
+      <c r="F41" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G41" t="str">
+        <v>19/08/2026, 15:34:59</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G41"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/payments.xlsx
+++ b/payments.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G47"/>
   <cols>
     <col min="1" max="1" width="28.83203125" customWidth="1"/>
     <col min="2" max="2" width="25.83203125" customWidth="1"/>
@@ -1351,9 +1351,147 @@
         <v>19/08/2026, 15:34:59</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B42" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C42">
+        <v>0</v>
+      </c>
+      <c r="D42">
+        <v>10</v>
+      </c>
+      <c r="E42" t="str">
+        <v>680</v>
+      </c>
+      <c r="F42" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G42" t="str">
+        <v>21/08/2026, 14:17:49</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B43" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C43">
+        <v>0</v>
+      </c>
+      <c r="D43">
+        <v>10</v>
+      </c>
+      <c r="E43" t="str">
+        <v>670</v>
+      </c>
+      <c r="F43" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G43" t="str">
+        <v>21/08/2026, 15:47:32</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B44" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C44">
+        <v>0</v>
+      </c>
+      <c r="D44">
+        <v>10</v>
+      </c>
+      <c r="E44" t="str">
+        <v>660</v>
+      </c>
+      <c r="F44" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G44" t="str">
+        <v>21/08/2026, 17:49:03</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B45" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C45">
+        <v>0</v>
+      </c>
+      <c r="D45">
+        <v>10</v>
+      </c>
+      <c r="E45" t="str">
+        <v>650</v>
+      </c>
+      <c r="F45" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G45" t="str">
+        <v>21/08/2026, 17:49:38</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B46" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C46">
+        <v>0</v>
+      </c>
+      <c r="D46">
+        <v>10</v>
+      </c>
+      <c r="E46" t="str">
+        <v>640</v>
+      </c>
+      <c r="F46" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G46" t="str">
+        <v>21/08/2026, 17:52:54</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B47" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C47">
+        <v>0</v>
+      </c>
+      <c r="D47">
+        <v>10</v>
+      </c>
+      <c r="E47" t="str">
+        <v>630</v>
+      </c>
+      <c r="F47" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G47" t="str">
+        <v>21/08/2026, 17:54:00</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G41"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G47"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/payments.xlsx
+++ b/payments.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:G67"/>
   <cols>
     <col min="1" max="1" width="28.83203125" customWidth="1"/>
     <col min="2" max="2" width="25.83203125" customWidth="1"/>
@@ -1489,9 +1489,469 @@
         <v>21/08/2026, 17:54:00</v>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B48" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C48">
+        <v>0</v>
+      </c>
+      <c r="D48">
+        <v>10</v>
+      </c>
+      <c r="E48" t="str">
+        <v>620</v>
+      </c>
+      <c r="F48" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G48" t="str">
+        <v>24/08/2026, 13:53:19</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B49" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C49">
+        <v>0</v>
+      </c>
+      <c r="D49">
+        <v>10</v>
+      </c>
+      <c r="E49" t="str">
+        <v>610</v>
+      </c>
+      <c r="F49" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G49" t="str">
+        <v>24/08/2026, 13:55:41</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B50" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C50">
+        <v>0</v>
+      </c>
+      <c r="D50">
+        <v>10</v>
+      </c>
+      <c r="E50" t="str">
+        <v>600</v>
+      </c>
+      <c r="F50" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G50" t="str">
+        <v>24/08/2026, 13:57:38</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B51" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C51">
+        <v>0</v>
+      </c>
+      <c r="D51">
+        <v>10</v>
+      </c>
+      <c r="E51" t="str">
+        <v>590</v>
+      </c>
+      <c r="F51" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G51" t="str">
+        <v>24/08/2026, 13:58:29</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B52" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C52">
+        <v>0</v>
+      </c>
+      <c r="D52">
+        <v>10</v>
+      </c>
+      <c r="E52" t="str">
+        <v>580</v>
+      </c>
+      <c r="F52" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G52" t="str">
+        <v>24/08/2026, 14:06:01</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B53" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C53">
+        <v>0</v>
+      </c>
+      <c r="D53">
+        <v>10</v>
+      </c>
+      <c r="E53" t="str">
+        <v>570</v>
+      </c>
+      <c r="F53" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G53" t="str">
+        <v>24/08/2026, 14:08:14</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B54" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C54">
+        <v>0</v>
+      </c>
+      <c r="D54">
+        <v>10</v>
+      </c>
+      <c r="E54" t="str">
+        <v>560</v>
+      </c>
+      <c r="F54" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G54" t="str">
+        <v>24/08/2026, 14:11:46</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B55" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C55">
+        <v>0</v>
+      </c>
+      <c r="D55">
+        <v>10</v>
+      </c>
+      <c r="E55" t="str">
+        <v>550</v>
+      </c>
+      <c r="F55" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G55" t="str">
+        <v>24/08/2026, 14:17:41</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B56" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C56">
+        <v>0</v>
+      </c>
+      <c r="D56">
+        <v>10</v>
+      </c>
+      <c r="E56" t="str">
+        <v>540</v>
+      </c>
+      <c r="F56" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G56" t="str">
+        <v>24/08/2026, 14:19:19</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B57" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C57">
+        <v>0</v>
+      </c>
+      <c r="D57">
+        <v>10</v>
+      </c>
+      <c r="E57" t="str">
+        <v>530</v>
+      </c>
+      <c r="F57" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G57" t="str">
+        <v>24/08/2026, 14:20:33</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B58" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C58">
+        <v>0</v>
+      </c>
+      <c r="D58">
+        <v>10</v>
+      </c>
+      <c r="E58" t="str">
+        <v>520</v>
+      </c>
+      <c r="F58" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G58" t="str">
+        <v>24/08/2026, 14:21:58</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B59" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C59">
+        <v>0</v>
+      </c>
+      <c r="D59">
+        <v>10</v>
+      </c>
+      <c r="E59" t="str">
+        <v>510</v>
+      </c>
+      <c r="F59" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G59" t="str">
+        <v>24/08/2026, 14:39:21</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B60" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C60">
+        <v>0</v>
+      </c>
+      <c r="D60">
+        <v>10</v>
+      </c>
+      <c r="E60" t="str">
+        <v>500</v>
+      </c>
+      <c r="F60" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G60" t="str">
+        <v>24/08/2026, 14:45:56</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B61" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C61">
+        <v>0</v>
+      </c>
+      <c r="D61">
+        <v>10</v>
+      </c>
+      <c r="E61" t="str">
+        <v>490</v>
+      </c>
+      <c r="F61" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G61" t="str">
+        <v>24/08/2026, 15:09:06</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B62" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C62">
+        <v>0</v>
+      </c>
+      <c r="D62">
+        <v>10</v>
+      </c>
+      <c r="E62" t="str">
+        <v>480</v>
+      </c>
+      <c r="F62" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G62" t="str">
+        <v>24/08/2026, 15:39:54</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B63" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C63">
+        <v>0</v>
+      </c>
+      <c r="D63">
+        <v>10</v>
+      </c>
+      <c r="E63" t="str">
+        <v>470</v>
+      </c>
+      <c r="F63" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G63" t="str">
+        <v>24/08/2026, 15:41:49</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B64" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C64">
+        <v>0</v>
+      </c>
+      <c r="D64">
+        <v>10</v>
+      </c>
+      <c r="E64" t="str">
+        <v>460</v>
+      </c>
+      <c r="F64" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G64" t="str">
+        <v>24/08/2026, 16:15:23</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B65" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C65">
+        <v>0</v>
+      </c>
+      <c r="D65">
+        <v>10</v>
+      </c>
+      <c r="E65" t="str">
+        <v>450</v>
+      </c>
+      <c r="F65" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G65" t="str">
+        <v>24/08/2026, 16:18:34</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B66" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C66">
+        <v>0</v>
+      </c>
+      <c r="D66">
+        <v>10</v>
+      </c>
+      <c r="E66" t="str">
+        <v>440</v>
+      </c>
+      <c r="F66" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G66" t="str">
+        <v>24/08/2026, 16:19:47</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B67" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C67">
+        <v>0</v>
+      </c>
+      <c r="D67">
+        <v>10</v>
+      </c>
+      <c r="E67" t="str">
+        <v>430</v>
+      </c>
+      <c r="F67" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G67" t="str">
+        <v>24/08/2026, 16:20:08</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G47"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G67"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/payments.xlsx
+++ b/payments.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:G69"/>
   <cols>
     <col min="1" max="1" width="28.83203125" customWidth="1"/>
     <col min="2" max="2" width="25.83203125" customWidth="1"/>
@@ -1949,9 +1949,55 @@
         <v>24/08/2026, 16:20:08</v>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B68" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C68">
+        <v>0</v>
+      </c>
+      <c r="D68">
+        <v>10</v>
+      </c>
+      <c r="E68" t="str">
+        <v>420</v>
+      </c>
+      <c r="F68" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G68" t="str">
+        <v>24/08/2026, 20:02:01</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="B69" t="str">
+        <v>unknowne1931</v>
+      </c>
+      <c r="C69">
+        <v>0</v>
+      </c>
+      <c r="D69">
+        <v>10</v>
+      </c>
+      <c r="E69" t="str">
+        <v>410</v>
+      </c>
+      <c r="F69" t="str">
+        <v>To start Mili Game</v>
+      </c>
+      <c r="G69" t="str">
+        <v>24/08/2026, 20:03:34</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G67"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G69"/>
   </ignoredErrors>
 </worksheet>
 </file>